--- a/frontend/public/download_SP.xlsx
+++ b/frontend/public/download_SP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ngoc Thai\pharmacy-fullstack-project\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D725687-9987-4719-9FCF-1192845B4F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E527A7-CF7B-4F18-8E79-8C40659BD73A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4536,7 +4536,8 @@
   <dimension ref="A1:I360"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.625" customWidth="1"/>
     <col min="6" max="6" width="13.625" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
@@ -6080,7 +6081,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>250</v>
       </c>
@@ -6602,7 +6603,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>325</v>
       </c>
@@ -6631,7 +6632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>328</v>
       </c>
